--- a/excel/butterScaler/butterScaler23-Section04.xlsx
+++ b/excel/butterScaler/butterScaler23-Section04.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10331"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10407"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{770A5A58-F244-9A40-9F2D-E41993D57E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45EF153-96A4-034A-8097-6C5DA76CBCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{037420B4-A38F-504D-A618-656DC2DF4E91}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="73">
   <si>
     <t>ActionName</t>
   </si>
@@ -236,13 +236,16 @@
   </si>
   <si>
     <t>结束</t>
+  </si>
+  <si>
+    <t>StepActionName</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -377,6 +380,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -559,7 +568,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -674,6 +683,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -719,8 +743,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1096,1268 +1124,1280 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EE61FC-090D-8D4D-8A8E-6AB41B1B973A}">
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
         <v>9</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" t="b">
+      <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>16</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>18</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
         <v>17</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>18</v>
       </c>
-      <c r="F9" t="b">
+      <c r="G9" t="b">
         <v>1</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>19</v>
       </c>
-      <c r="H9" t="b">
+      <c r="I9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10">
         <v>10</v>
       </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>21</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>21</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
       <c r="B12">
         <v>10</v>
       </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
         <v>20</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>21</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13">
         <v>10</v>
       </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
         <v>20</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>21</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14">
         <v>10</v>
       </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
         <v>20</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>21</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15">
         <v>10</v>
       </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" t="s">
         <v>20</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>21</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16">
         <v>10</v>
       </c>
-      <c r="C16">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
         <v>22</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>23</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>19</v>
       </c>
       <c r="B17">
         <v>10</v>
       </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" t="s">
         <v>22</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>23</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18">
         <v>10</v>
       </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18" t="s">
         <v>24</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>25</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19">
         <v>10</v>
       </c>
-      <c r="C19">
-        <v>4</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
         <v>24</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>25</v>
       </c>
-      <c r="F19" t="b">
+      <c r="G19" t="b">
         <v>1</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>26</v>
       </c>
-      <c r="H19" t="b">
+      <c r="I19" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>26</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
-      <c r="C20">
-        <v>4</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
         <v>27</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>28</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>26</v>
       </c>
       <c r="B21">
         <v>4</v>
       </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21" t="s">
         <v>27</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>28</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>26</v>
       </c>
       <c r="B22">
         <v>4</v>
       </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
         <v>29</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>30</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23">
         <v>4</v>
       </c>
-      <c r="C23">
-        <v>4</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
         <v>29</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>30</v>
       </c>
-      <c r="F23" t="b">
+      <c r="G23" t="b">
         <v>1</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>31</v>
       </c>
-      <c r="H23" t="b">
+      <c r="I23" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>31</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
-      <c r="C24">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24" t="s">
         <v>32</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>33</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>31</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
-      <c r="C25">
-        <v>4</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25" t="s">
         <v>34</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>35</v>
       </c>
-      <c r="F25" t="b">
+      <c r="G25" t="b">
         <v>1</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>36</v>
       </c>
-      <c r="H25" t="b">
+      <c r="I25" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>36</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
-      <c r="C26">
-        <v>4</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
         <v>37</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>38</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>36</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
-      <c r="C27">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27" t="s">
         <v>37</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>39</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>36</v>
       </c>
       <c r="B28">
         <v>4</v>
       </c>
-      <c r="C28">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28" t="s">
         <v>37</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>40</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>36</v>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
-      <c r="C29">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
         <v>37</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>41</v>
       </c>
-      <c r="F29" t="b">
+      <c r="G29" t="b">
         <v>1</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>42</v>
       </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>42</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
-      <c r="C30">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30" t="s">
         <v>43</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>16</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>42</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
-      <c r="C31">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31" t="s">
         <v>43</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>44</v>
       </c>
-      <c r="F31" t="b">
+      <c r="G31" t="b">
         <v>1</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>45</v>
       </c>
-      <c r="H31" t="b">
+      <c r="I31" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>46</v>
       </c>
       <c r="B32">
         <v>4</v>
       </c>
-      <c r="C32">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
         <v>47</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>48</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>46</v>
       </c>
       <c r="B33">
         <v>4</v>
       </c>
-      <c r="C33">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33" t="s">
         <v>47</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>48</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>46</v>
       </c>
       <c r="B34">
         <v>4</v>
       </c>
-      <c r="C34">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34" t="s">
         <v>49</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>50</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>46</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
-      <c r="C35">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35" t="s">
         <v>49</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>50</v>
       </c>
-      <c r="F35" t="b">
+      <c r="G35" t="b">
         <v>1</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>51</v>
       </c>
-      <c r="H35" t="b">
+      <c r="I35" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>52</v>
       </c>
       <c r="B36">
         <v>4</v>
       </c>
-      <c r="C36">
-        <v>4</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36" t="s">
         <v>53</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>54</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>52</v>
       </c>
       <c r="B37">
         <v>4</v>
       </c>
-      <c r="C37">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37" t="s">
         <v>53</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>54</v>
       </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>52</v>
       </c>
       <c r="B38">
         <v>4</v>
       </c>
-      <c r="C38">
-        <v>4</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38" t="s">
         <v>17</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>55</v>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>52</v>
       </c>
       <c r="B39">
         <v>4</v>
       </c>
-      <c r="C39">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
         <v>17</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>55</v>
       </c>
-      <c r="F39" t="b">
+      <c r="G39" t="b">
         <v>1</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>56</v>
       </c>
-      <c r="H39" t="b">
+      <c r="I39" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>42</v>
       </c>
       <c r="B40">
         <v>6</v>
       </c>
-      <c r="C40">
-        <v>4</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40" t="s">
         <v>43</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>57</v>
       </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>42</v>
       </c>
       <c r="B41">
         <v>6</v>
       </c>
-      <c r="C41">
-        <v>4</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
         <v>43</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>57</v>
       </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>42</v>
       </c>
       <c r="B42">
         <v>6</v>
       </c>
-      <c r="C42">
-        <v>4</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42" t="s">
         <v>58</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>59</v>
       </c>
-      <c r="F42" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>42</v>
       </c>
       <c r="B43">
         <v>6</v>
       </c>
-      <c r="C43">
-        <v>4</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43" t="s">
         <v>58</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>59</v>
       </c>
-      <c r="F43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>42</v>
       </c>
       <c r="B44">
         <v>6</v>
       </c>
-      <c r="C44">
-        <v>4</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44" t="s">
         <v>60</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>61</v>
       </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>42</v>
       </c>
       <c r="B45">
         <v>6</v>
       </c>
-      <c r="C45">
-        <v>4</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="D45">
+        <v>4</v>
+      </c>
+      <c r="E45" t="s">
         <v>60</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>61</v>
       </c>
-      <c r="F45" t="b">
+      <c r="G45" t="b">
         <v>1</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>62</v>
       </c>
-      <c r="H45" t="b">
+      <c r="I45" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>46</v>
       </c>
       <c r="B46">
         <v>4</v>
       </c>
-      <c r="C46">
-        <v>4</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46" t="s">
         <v>47</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>63</v>
       </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>46</v>
       </c>
       <c r="B47">
         <v>4</v>
       </c>
-      <c r="C47">
-        <v>4</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47" t="s">
         <v>47</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>63</v>
       </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>46</v>
       </c>
       <c r="B48">
         <v>4</v>
       </c>
-      <c r="C48">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="E48" t="s">
         <v>64</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>65</v>
       </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>46</v>
       </c>
       <c r="B49">
         <v>4</v>
       </c>
-      <c r="C49">
-        <v>4</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49" t="s">
         <v>64</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>65</v>
       </c>
-      <c r="F49" t="b">
+      <c r="G49" t="b">
         <v>1</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>66</v>
       </c>
-      <c r="H49" t="b">
+      <c r="I49" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>52</v>
       </c>
       <c r="B50">
         <v>4</v>
       </c>
-      <c r="C50">
-        <v>4</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
         <v>67</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>68</v>
       </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>52</v>
       </c>
       <c r="B51">
         <v>4</v>
       </c>
-      <c r="C51">
-        <v>4</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="D51">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
         <v>67</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>68</v>
       </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
-      <c r="H51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>52</v>
       </c>
       <c r="B52">
         <v>4</v>
       </c>
-      <c r="C52">
-        <v>4</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52" t="s">
         <v>69</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>70</v>
       </c>
-      <c r="F52" t="b">
-        <v>0</v>
-      </c>
-      <c r="H52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>52</v>
       </c>
       <c r="B53">
         <v>4</v>
       </c>
-      <c r="C53">
-        <v>4</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
         <v>69</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>70</v>
       </c>
-      <c r="F53" t="b">
+      <c r="G53" t="b">
         <v>1</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>71</v>
       </c>
-      <c r="H53" t="b">
+      <c r="I53" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{2988f0a4-524a-45f2-829d-417725fa4957}" enabled="1" method="Standard" siteId="{52daf2a9-3b73-4da4-ac6a-3f81adc92b7e}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/excel/butterScaler/butterScaler23-Section04.xlsx
+++ b/excel/butterScaler/butterScaler23-Section04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45EF153-96A4-034A-8097-6C5DA76CBCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2FD544-97FE-6E4A-9563-6677377BB131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{037420B4-A38F-504D-A618-656DC2DF4E91}"/>
+    <workbookView xWindow="-3180" yWindow="-18840" windowWidth="28040" windowHeight="17180" xr2:uid="{037420B4-A38F-504D-A618-656DC2DF4E91}"/>
   </bookViews>
   <sheets>
     <sheet name="fitness_course4_detailed" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="105">
   <si>
     <t>ActionName</t>
   </si>
@@ -46,206 +46,302 @@
     <t>RhythmAlert</t>
   </si>
   <si>
-    <t>四足式L</t>
-  </si>
-  <si>
-    <t>四足准备</t>
-  </si>
-  <si>
-    <t>右膝压弹力带，左腿伸直向后点地</t>
-  </si>
-  <si>
-    <t>第2个8拍，保持姿势</t>
-  </si>
-  <si>
-    <t>第3个8拍，保持姿势</t>
-  </si>
-  <si>
-    <t>第4个8拍，保持姿势</t>
-  </si>
-  <si>
-    <t>2/2抬腿L</t>
-  </si>
-  <si>
-    <t>2/2慢速抬腿</t>
-  </si>
-  <si>
-    <t>2拍抬起，2拍落下，控制节奏</t>
-  </si>
-  <si>
-    <t>保持控制</t>
-  </si>
-  <si>
-    <t>左腿后抬，稳定核心</t>
-  </si>
-  <si>
-    <t>1/1抬腿L</t>
-  </si>
-  <si>
-    <t>1/1快速抬腿</t>
-  </si>
-  <si>
-    <t>1拍抬起1拍落下，左腿后抬</t>
-  </si>
-  <si>
-    <t>保持频率</t>
-  </si>
-  <si>
-    <t>后腿开始悬空，持续抬腿</t>
-  </si>
-  <si>
-    <t>悬空保持</t>
-  </si>
-  <si>
-    <t>后腿不落地，持续高频</t>
-  </si>
-  <si>
-    <t>3p/s抬腿L</t>
-  </si>
-  <si>
-    <t>3拍一次抬腿</t>
-  </si>
-  <si>
-    <t>3拍完成一次抬腿，控制速度</t>
-  </si>
-  <si>
-    <t>保持节奏</t>
-  </si>
-  <si>
-    <t>3p/s模式，稳定控制</t>
-  </si>
-  <si>
-    <t>8p/s抬腿L</t>
-  </si>
-  <si>
-    <t>8拍超慢速</t>
-  </si>
-  <si>
-    <t>8拍完成一次，极限控制</t>
-  </si>
-  <si>
-    <t>最高点保持</t>
-  </si>
-  <si>
-    <t>停在最高点，准备换动作</t>
-  </si>
-  <si>
     <t>仰卧</t>
   </si>
   <si>
-    <t>仰卧准备</t>
-  </si>
-  <si>
-    <t>弹力带膝盖上方，双腿向外打开，保持张力</t>
-  </si>
-  <si>
-    <t>第2个8拍，保持稳定</t>
-  </si>
-  <si>
-    <t>第3个8拍，保持稳定</t>
-  </si>
-  <si>
-    <t>第4个8拍，保持稳定</t>
-  </si>
-  <si>
-    <t>2/2臀桥</t>
-  </si>
-  <si>
-    <t>2/2慢速臀桥</t>
-  </si>
-  <si>
-    <t>保持臀部收紧，不触地</t>
-  </si>
-  <si>
-    <t>1/1臀桥-第一段</t>
-  </si>
-  <si>
-    <t>1/1臀桥</t>
-  </si>
-  <si>
-    <t>1/1快速臀桥</t>
-  </si>
-  <si>
-    <t>1拍抬起1拍落下，加快速度</t>
-  </si>
-  <si>
-    <t>加速节奏</t>
-  </si>
-  <si>
-    <t>快速模式，激活臀部</t>
-  </si>
-  <si>
-    <t>3p/s臀桥-第一段</t>
-  </si>
-  <si>
-    <t>3p/s臀桥</t>
-  </si>
-  <si>
-    <t>3拍一次臀桥</t>
-  </si>
-  <si>
-    <t>3拍完成一次，中速控制</t>
-  </si>
-  <si>
-    <t>3p/s模式，持续张力</t>
-  </si>
-  <si>
-    <t>2/2臀桥-第二段</t>
-  </si>
-  <si>
-    <t>回到慢速，2拍一动</t>
-  </si>
-  <si>
-    <t>悬停模式</t>
-  </si>
-  <si>
-    <t>臀部最低点不触地</t>
-  </si>
-  <si>
-    <t>持续悬空</t>
-  </si>
-  <si>
-    <t>全程保持，不落地</t>
-  </si>
-  <si>
-    <t>1/1臀桥-第二段</t>
-  </si>
-  <si>
-    <t>高频臀桥，保持悬空</t>
-  </si>
-  <si>
-    <t>冲刺阶段</t>
-  </si>
-  <si>
-    <t>最后加速，准备结束</t>
-  </si>
-  <si>
-    <t>3p/s臀桥-第二段</t>
-  </si>
-  <si>
-    <t>3拍控制</t>
-  </si>
-  <si>
-    <t>中速控制，持续发力</t>
-  </si>
-  <si>
-    <t>最后保持</t>
-  </si>
-  <si>
-    <t>课程即将结束</t>
+    <t>StepActionName</t>
+  </si>
+  <si>
+    <t>双膝跪地，膝盖与髋同宽</t>
+  </si>
+  <si>
+    <t>保持挺胸</t>
+  </si>
+  <si>
+    <t>双手停在你的肩膀正下方</t>
+  </si>
+  <si>
+    <t>稳定好之后</t>
+  </si>
+  <si>
+    <t>伸直右腿</t>
+  </si>
+  <si>
+    <t>伸直右腿，双手压住垫子</t>
+  </si>
+  <si>
+    <t>眼睛看向正前方</t>
+  </si>
+  <si>
+    <t>接来下，直腿上抬</t>
+  </si>
+  <si>
+    <t>2拍起</t>
+  </si>
+  <si>
+    <t>大腿抬到平齐地板的位置</t>
+  </si>
+  <si>
+    <t>脚跟身体连成一条线</t>
+  </si>
+  <si>
+    <t>1次抬腿</t>
+  </si>
+  <si>
+    <t>接下来做激活</t>
+  </si>
+  <si>
+    <t>准备加快</t>
+  </si>
+  <si>
+    <t>让你的双手稳定</t>
+  </si>
+  <si>
+    <t>手用力推住地板</t>
+  </si>
+  <si>
+    <t>每一次的抬起</t>
+  </si>
+  <si>
+    <t>减少大腿的参与</t>
+  </si>
+  <si>
+    <t>感受臀部肌肉发力</t>
+  </si>
+  <si>
+    <t>还有4次</t>
+  </si>
+  <si>
+    <t>向下脚尖轻点地</t>
+  </si>
+  <si>
+    <t>准备好了，提升强度</t>
+  </si>
+  <si>
+    <t>向下只落一半</t>
+  </si>
+  <si>
+    <t>上抬，落一半</t>
+  </si>
+  <si>
+    <t>如果累了，继续脚尖落地</t>
+  </si>
+  <si>
+    <t>如果可以，尝试停的久一点</t>
+  </si>
+  <si>
+    <t>节奏放慢</t>
+  </si>
+  <si>
+    <t>停在高处</t>
+  </si>
+  <si>
+    <t>准备三次弹动</t>
+  </si>
+  <si>
+    <t>2次抬腿</t>
+  </si>
+  <si>
+    <t>2次抬腿落一半</t>
+  </si>
+  <si>
+    <t>3次弹动</t>
+  </si>
+  <si>
+    <t>8次弹动</t>
+  </si>
+  <si>
+    <t>3，2，1</t>
+  </si>
+  <si>
+    <t>停住慢落</t>
+  </si>
+  <si>
+    <t>加上停顿</t>
+  </si>
+  <si>
+    <t>也是顶峰收缩</t>
+  </si>
+  <si>
+    <t>最后一次</t>
+  </si>
+  <si>
+    <t>快速转身仰卧</t>
+  </si>
+  <si>
+    <t>我们把肚子绷紧</t>
+  </si>
+  <si>
+    <t>弹力绳回到膝盖的上方</t>
+  </si>
+  <si>
+    <t>脚跟踩在膝盖的正下方</t>
+  </si>
+  <si>
+    <t>拿起负重片</t>
+  </si>
+  <si>
+    <t>躺在垫子</t>
+  </si>
+  <si>
+    <t>慢速臀桥</t>
+  </si>
+  <si>
+    <t>2拍起，2拍下</t>
+  </si>
+  <si>
+    <t>踩稳之后，挺胸</t>
+  </si>
+  <si>
+    <t>一起加速</t>
+  </si>
+  <si>
+    <t>让你的髋关节垂直向上</t>
+  </si>
+  <si>
+    <t>推到肩髋膝一条线的位置</t>
+  </si>
+  <si>
+    <t>呼，推，呼，推</t>
+  </si>
+  <si>
+    <t>准备好换个节奏</t>
+  </si>
+  <si>
+    <t>停在高处，3次往上</t>
+  </si>
+  <si>
+    <t>3次弹动抬腿</t>
+  </si>
+  <si>
+    <t>8次弹动抬腿</t>
+  </si>
+  <si>
+    <t>臀桥3次弹动</t>
+  </si>
+  <si>
+    <t>臀桥1次</t>
+  </si>
+  <si>
+    <t>臀桥2次</t>
+  </si>
+  <si>
+    <t>3，2，1，停</t>
+  </si>
+  <si>
+    <t>让你的脚跟用力蹬向地板</t>
+  </si>
+  <si>
+    <t>这里开始</t>
+  </si>
+  <si>
+    <t>2拍向上</t>
+  </si>
+  <si>
+    <t>接下来，我们要完成</t>
+  </si>
+  <si>
+    <t>一半悬空</t>
+  </si>
+  <si>
+    <t>臀桥1次悬空</t>
+  </si>
+  <si>
+    <t>臀部不要触地</t>
+  </si>
+  <si>
+    <t>保持悬空完成</t>
+  </si>
+  <si>
+    <t>如果累了</t>
+  </si>
+  <si>
+    <t>可以触地休息</t>
+  </si>
+  <si>
+    <t>我们把节奏再放慢一点</t>
+  </si>
+  <si>
+    <t>虽然很酸，但我们再加快一点</t>
+  </si>
+  <si>
+    <t>让你的脚跟依旧用力蹬地板</t>
+  </si>
+  <si>
+    <t>用力的挺胸向上</t>
+  </si>
+  <si>
+    <t>用一个稳固的姿势来完成</t>
+  </si>
+  <si>
+    <t>准备好了么</t>
+  </si>
+  <si>
+    <t>四足式</t>
+  </si>
+  <si>
+    <t>3，2，1，向下</t>
+  </si>
+  <si>
+    <t>我们再来2次</t>
+  </si>
+  <si>
+    <t>预先准备</t>
+  </si>
+  <si>
+    <t>右腿1次抬腿</t>
+  </si>
+  <si>
+    <t>右腿2次抬腿</t>
+  </si>
+  <si>
+    <t>右腿2次抬腿落一半</t>
+  </si>
+  <si>
+    <t>右腿3次弹动抬腿</t>
+  </si>
+  <si>
+    <t>右腿8次弹动抬腿</t>
+  </si>
+  <si>
+    <t>伸直左腿</t>
+  </si>
+  <si>
+    <t>左腿1次抬腿</t>
+  </si>
+  <si>
+    <t>左腿2次抬腿</t>
+  </si>
+  <si>
+    <t>左腿2次抬腿落一半</t>
+  </si>
+  <si>
+    <t>左腿3次弹动抬腿</t>
+  </si>
+  <si>
+    <t>左腿8次弹动抬腿</t>
+  </si>
+  <si>
+    <t>勾住脚尖</t>
+  </si>
+  <si>
+    <t>如果可以，勾住脚尖</t>
+  </si>
+  <si>
+    <t>我们一起做半程</t>
+  </si>
+  <si>
+    <t>保持悬空</t>
   </si>
   <si>
     <t>结束</t>
-  </si>
-  <si>
-    <t>StepActionName</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -385,6 +481,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -743,12 +846,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1124,10 +1228,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EE61FC-090D-8D4D-8A8E-6AB41B1B973A}">
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1138,7 +1250,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -1161,19 +1273,22 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="B2">
         <v>4</v>
       </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
       <c r="D2">
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -1184,19 +1299,22 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="B3">
         <v>4</v>
       </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
       <c r="D3">
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -1207,19 +1325,22 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
       <c r="D4">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -1230,25 +1351,28 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -1256,19 +1380,19 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
       <c r="D6">
         <v>4</v>
       </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
+      <c r="E6">
+        <v>1221</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -1279,19 +1403,19 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
+      <c r="C7" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -1302,19 +1426,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -1325,45 +1449,48 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
+      <c r="C9" t="s">
+        <v>89</v>
+      </c>
       <c r="D9">
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="I9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>21</v>
+      <c r="E10">
+        <v>1212</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -1374,19 +1501,22 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -1397,19 +1527,22 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B12">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
@@ -1420,19 +1553,22 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B13">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
@@ -1443,19 +1579,22 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="D14">
         <v>4</v>
       </c>
-      <c r="E14" t="s">
-        <v>20</v>
+      <c r="E14">
+        <v>1212</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -1466,22 +1605,28 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B15">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G15" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>40</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -1489,19 +1634,22 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
@@ -1512,19 +1660,19 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
@@ -1535,19 +1683,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="D18">
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
@@ -1558,45 +1709,51 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B19">
-        <v>10</v>
+        <v>4</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="D19">
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="I19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
+      <c r="C20" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G20" t="b">
         <v>0</v>
@@ -1607,19 +1764,22 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="B21">
         <v>4</v>
       </c>
+      <c r="C21" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G21" t="b">
         <v>0</v>
@@ -1630,19 +1790,19 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="B22">
         <v>4</v>
       </c>
+      <c r="C22" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="G22" t="b">
         <v>0</v>
@@ -1653,45 +1813,48 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="B23">
         <v>4</v>
       </c>
+      <c r="C23" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="D23">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="I23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
+      <c r="C24" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="D24">
         <v>4</v>
       </c>
-      <c r="E24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" t="s">
-        <v>33</v>
+      <c r="E24">
+        <v>8765</v>
       </c>
       <c r="G24" t="b">
         <v>0</v>
@@ -1702,45 +1865,48 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
+      <c r="C25" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="D25">
         <v>4</v>
       </c>
-      <c r="E25" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" t="s">
-        <v>35</v>
+      <c r="E25">
+        <v>4321</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="I25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G26" t="b">
         <v>0</v>
@@ -1751,19 +1917,22 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F27" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G27" t="b">
         <v>0</v>
@@ -1774,19 +1943,19 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B28">
         <v>4</v>
       </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
       <c r="D28">
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
-      </c>
-      <c r="F28" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G28" t="b">
         <v>0</v>
@@ -1797,25 +1966,28 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
       <c r="D29">
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -1823,19 +1995,19 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
+      <c r="C30" t="s">
+        <v>66</v>
+      </c>
       <c r="D30">
         <v>4</v>
       </c>
-      <c r="E30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" t="s">
-        <v>16</v>
+      <c r="E30">
+        <v>1221</v>
       </c>
       <c r="G30" t="b">
         <v>0</v>
@@ -1846,45 +2018,48 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
+      <c r="C31" t="s">
+        <v>66</v>
+      </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F31" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="I31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B32">
         <v>4</v>
       </c>
+      <c r="C32" t="s">
+        <v>67</v>
+      </c>
       <c r="D32">
         <v>4</v>
       </c>
-      <c r="E32" t="s">
-        <v>47</v>
-      </c>
-      <c r="F32" t="s">
-        <v>48</v>
+      <c r="E32">
+        <v>1212</v>
       </c>
       <c r="G32" t="b">
         <v>0</v>
@@ -1895,19 +2070,22 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B33">
         <v>4</v>
       </c>
+      <c r="C33" t="s">
+        <v>67</v>
+      </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="F33" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G33" t="b">
         <v>0</v>
@@ -1918,19 +2096,19 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B34">
         <v>4</v>
       </c>
+      <c r="C34" t="s">
+        <v>67</v>
+      </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>49</v>
-      </c>
-      <c r="F34" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G34" t="b">
         <v>0</v>
@@ -1941,45 +2119,48 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
+      <c r="C35" t="s">
+        <v>67</v>
+      </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F35" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="I35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B36">
         <v>4</v>
       </c>
+      <c r="C36" t="s">
+        <v>65</v>
+      </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G36" t="b">
         <v>0</v>
@@ -1990,19 +2171,19 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B37">
         <v>4</v>
       </c>
+      <c r="C37" t="s">
+        <v>65</v>
+      </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
-      </c>
-      <c r="F37" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G37" t="b">
         <v>0</v>
@@ -2013,19 +2194,19 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B38">
         <v>4</v>
       </c>
+      <c r="C38" t="s">
+        <v>65</v>
+      </c>
       <c r="D38">
         <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="G38" t="b">
         <v>0</v>
@@ -2036,45 +2217,48 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B39">
         <v>4</v>
       </c>
+      <c r="C39" t="s">
+        <v>65</v>
+      </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="F39" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="C40" t="s">
+        <v>66</v>
       </c>
       <c r="D40">
         <v>4</v>
       </c>
-      <c r="E40" t="s">
-        <v>43</v>
-      </c>
-      <c r="F40" t="s">
-        <v>57</v>
+      <c r="E40">
+        <v>1221</v>
       </c>
       <c r="G40" t="b">
         <v>0</v>
@@ -2085,42 +2269,51 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B41">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>66</v>
       </c>
       <c r="D41">
         <v>4</v>
       </c>
       <c r="E41" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="F41" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="G41" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>42</v>
+      <c r="A42" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G42" t="b">
         <v>0</v>
@@ -2130,20 +2323,23 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>42</v>
+      <c r="A43" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B43">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="D43">
         <v>4</v>
       </c>
       <c r="E43" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="F43" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="G43" t="b">
         <v>0</v>
@@ -2153,20 +2349,20 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>42</v>
+      <c r="A44" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B44">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="D44">
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>60</v>
-      </c>
-      <c r="F44" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="G44" t="b">
         <v>0</v>
@@ -2176,46 +2372,46 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>42</v>
+      <c r="A45" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B45">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="D45">
         <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>60</v>
-      </c>
-      <c r="F45" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B46">
         <v>4</v>
       </c>
+      <c r="C46" t="s">
+        <v>67</v>
+      </c>
       <c r="D46">
         <v>4</v>
       </c>
-      <c r="E46" t="s">
-        <v>47</v>
-      </c>
-      <c r="F46" t="s">
-        <v>63</v>
+      <c r="E46">
+        <v>1212</v>
       </c>
       <c r="G46" t="b">
         <v>0</v>
@@ -2226,19 +2422,22 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B47">
         <v>4</v>
       </c>
+      <c r="C47" t="s">
+        <v>67</v>
+      </c>
       <c r="D47">
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F47" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="G47" t="b">
         <v>0</v>
@@ -2249,19 +2448,19 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B48">
         <v>4</v>
       </c>
+      <c r="C48" t="s">
+        <v>67</v>
+      </c>
       <c r="D48">
         <v>4</v>
       </c>
       <c r="E48" t="s">
-        <v>64</v>
-      </c>
-      <c r="F48" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G48" t="b">
         <v>0</v>
@@ -2272,45 +2471,48 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B49">
         <v>4</v>
       </c>
+      <c r="C49" t="s">
+        <v>67</v>
+      </c>
       <c r="D49">
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F49" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="G49" t="b">
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B50">
         <v>4</v>
       </c>
+      <c r="C50" t="s">
+        <v>65</v>
+      </c>
       <c r="D50">
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F50" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="G50" t="b">
         <v>0</v>
@@ -2321,19 +2523,19 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B51">
         <v>4</v>
       </c>
+      <c r="C51" t="s">
+        <v>65</v>
+      </c>
       <c r="D51">
         <v>4</v>
       </c>
       <c r="E51" t="s">
-        <v>67</v>
-      </c>
-      <c r="F51" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="G51" t="b">
         <v>0</v>
@@ -2344,19 +2546,22 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B52">
         <v>4</v>
       </c>
+      <c r="C52" t="s">
+        <v>65</v>
+      </c>
       <c r="D52">
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="F52" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G52" t="b">
         <v>0</v>
@@ -2367,28 +2572,1359 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B53">
         <v>4</v>
       </c>
+      <c r="C53" t="s">
+        <v>65</v>
+      </c>
       <c r="D53">
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>69</v>
-      </c>
-      <c r="F53" t="s">
-        <v>70</v>
+        <v>47</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
       </c>
-      <c r="H53" t="s">
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+      <c r="E54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>85</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>88</v>
+      </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>88</v>
+      </c>
+      <c r="D56">
+        <v>4</v>
+      </c>
+      <c r="E56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>85</v>
+      </c>
+      <c r="B57">
+        <v>4</v>
+      </c>
+      <c r="C57" t="s">
+        <v>94</v>
+      </c>
+      <c r="D57">
+        <v>4</v>
+      </c>
+      <c r="E57" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="b">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58">
+        <v>4</v>
+      </c>
+      <c r="C58" t="s">
+        <v>95</v>
+      </c>
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58">
+        <v>1221</v>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B59">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>95</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" t="s">
+        <v>100</v>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>21</v>
+      </c>
+      <c r="B60">
+        <v>4</v>
+      </c>
+      <c r="C60" t="s">
+        <v>95</v>
+      </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>21</v>
+      </c>
+      <c r="B61">
+        <v>4</v>
+      </c>
+      <c r="C61" t="s">
+        <v>95</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="E61" t="s">
+        <v>22</v>
+      </c>
+      <c r="F61" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" t="s">
+        <v>39</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62">
+        <v>6</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62">
+        <v>1212</v>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63">
+        <v>6</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D63">
+        <v>4</v>
+      </c>
+      <c r="E63" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" t="s">
+        <v>25</v>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64">
+        <v>6</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64" t="s">
+        <v>26</v>
+      </c>
+      <c r="F64" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65">
+        <v>6</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D65">
+        <v>4</v>
+      </c>
+      <c r="E65" t="s">
+        <v>28</v>
+      </c>
+      <c r="F65" t="s">
+        <v>29</v>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66">
+        <v>6</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66">
+        <v>4</v>
+      </c>
+      <c r="E66">
+        <v>1212</v>
+      </c>
+      <c r="F66" t="s">
+        <v>30</v>
+      </c>
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+      <c r="E67" t="s">
+        <v>31</v>
+      </c>
+      <c r="F67" t="s">
+        <v>32</v>
+      </c>
+      <c r="G67" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
+        <v>40</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68">
+        <v>4</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68" t="s">
+        <v>33</v>
+      </c>
+      <c r="F68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>40</v>
+      </c>
+      <c r="B69">
+        <v>4</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69" t="s">
+        <v>34</v>
+      </c>
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>40</v>
+      </c>
+      <c r="B70">
+        <v>4</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70">
+        <v>4</v>
+      </c>
+      <c r="E70" t="s">
+        <v>101</v>
+      </c>
+      <c r="F70" t="s">
+        <v>36</v>
+      </c>
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>40</v>
+      </c>
+      <c r="B71">
+        <v>4</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71" t="s">
+        <v>37</v>
+      </c>
+      <c r="F71" t="s">
+        <v>38</v>
+      </c>
+      <c r="G71" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>63</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>63</v>
+      </c>
+      <c r="B72">
+        <v>4</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D72">
+        <v>4</v>
+      </c>
+      <c r="E72" t="s">
+        <v>68</v>
+      </c>
+      <c r="F72" t="s">
+        <v>44</v>
+      </c>
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73">
+        <v>4</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D73">
+        <v>4</v>
+      </c>
+      <c r="E73" t="s">
+        <v>45</v>
+      </c>
+      <c r="F73" t="s">
+        <v>46</v>
+      </c>
+      <c r="G73" t="b">
+        <v>0</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74">
+        <v>4</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74" t="s">
+        <v>49</v>
+      </c>
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75">
+        <v>4</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D75">
+        <v>4</v>
+      </c>
+      <c r="E75" t="s">
+        <v>47</v>
+      </c>
+      <c r="F75" t="s">
+        <v>42</v>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" t="s">
+        <v>64</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76">
+        <v>2</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D76">
+        <v>4</v>
+      </c>
+      <c r="E76">
+        <v>8765</v>
+      </c>
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D77">
+        <v>4</v>
+      </c>
+      <c r="E77">
+        <v>4321</v>
+      </c>
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" t="s">
+        <v>8</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78">
+        <v>4</v>
+      </c>
+      <c r="E78" t="s">
+        <v>48</v>
+      </c>
+      <c r="F78" t="s">
+        <v>50</v>
+      </c>
+      <c r="G78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79">
+        <v>4</v>
+      </c>
+      <c r="C79" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79">
+        <v>4</v>
+      </c>
+      <c r="E79" t="s">
+        <v>51</v>
+      </c>
+      <c r="F79" t="s">
+        <v>52</v>
+      </c>
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80" t="s">
+        <v>56</v>
+      </c>
+      <c r="G80" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81">
+        <v>4</v>
+      </c>
+      <c r="E81" t="s">
+        <v>53</v>
+      </c>
+      <c r="F81" t="s">
+        <v>54</v>
+      </c>
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" t="s">
+        <v>66</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>66</v>
+      </c>
+      <c r="B82">
+        <v>2</v>
+      </c>
+      <c r="C82" t="s">
+        <v>66</v>
+      </c>
+      <c r="D82">
+        <v>4</v>
+      </c>
+      <c r="E82">
+        <v>1221</v>
+      </c>
+      <c r="G82" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>66</v>
+      </c>
+      <c r="B83">
+        <v>2</v>
+      </c>
+      <c r="C83" t="s">
+        <v>66</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83" t="s">
+        <v>55</v>
+      </c>
+      <c r="F83" t="s">
+        <v>57</v>
+      </c>
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" t="s">
+        <v>67</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>67</v>
+      </c>
+      <c r="B84">
+        <v>4</v>
+      </c>
+      <c r="C84" t="s">
+        <v>67</v>
+      </c>
+      <c r="D84">
+        <v>4</v>
+      </c>
+      <c r="E84">
+        <v>1212</v>
+      </c>
+      <c r="G84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>67</v>
+      </c>
+      <c r="B85">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
+        <v>67</v>
+      </c>
+      <c r="D85">
+        <v>4</v>
+      </c>
+      <c r="E85" t="s">
+        <v>58</v>
+      </c>
+      <c r="F85" t="s">
+        <v>59</v>
+      </c>
+      <c r="G85" t="b">
+        <v>0</v>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>67</v>
+      </c>
+      <c r="B86">
+        <v>4</v>
+      </c>
+      <c r="C86" t="s">
+        <v>67</v>
+      </c>
+      <c r="D86">
+        <v>4</v>
+      </c>
+      <c r="E86" t="s">
+        <v>60</v>
+      </c>
+      <c r="G86" t="b">
+        <v>0</v>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>67</v>
+      </c>
+      <c r="B87">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>67</v>
+      </c>
+      <c r="D87">
+        <v>4</v>
+      </c>
+      <c r="E87" t="s">
+        <v>61</v>
+      </c>
+      <c r="F87" t="s">
+        <v>62</v>
+      </c>
+      <c r="G87" t="b">
+        <v>1</v>
+      </c>
+      <c r="H87" t="s">
+        <v>65</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>65</v>
+      </c>
+      <c r="B88">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>65</v>
+      </c>
+      <c r="D88">
+        <v>4</v>
+      </c>
+      <c r="E88" t="s">
+        <v>68</v>
+      </c>
+      <c r="G88" t="b">
+        <v>0</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>65</v>
+      </c>
+      <c r="B89">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>65</v>
+      </c>
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89" t="s">
+        <v>68</v>
+      </c>
+      <c r="G89" t="b">
+        <v>0</v>
+      </c>
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>65</v>
+      </c>
+      <c r="B90">
+        <v>4</v>
+      </c>
+      <c r="C90" t="s">
+        <v>65</v>
+      </c>
+      <c r="D90">
+        <v>4</v>
+      </c>
+      <c r="E90" t="s">
+        <v>69</v>
+      </c>
+      <c r="G90" t="b">
+        <v>0</v>
+      </c>
+      <c r="I90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>65</v>
+      </c>
+      <c r="B91">
+        <v>4</v>
+      </c>
+      <c r="C91" t="s">
+        <v>65</v>
+      </c>
+      <c r="D91">
+        <v>4</v>
+      </c>
+      <c r="E91" t="s">
+        <v>70</v>
+      </c>
+      <c r="F91" t="s">
         <v>71</v>
       </c>
-      <c r="I53" t="b">
+      <c r="G91" t="b">
         <v>1</v>
+      </c>
+      <c r="H91" t="s">
+        <v>66</v>
+      </c>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>66</v>
+      </c>
+      <c r="B92">
+        <v>2</v>
+      </c>
+      <c r="C92" t="s">
+        <v>66</v>
+      </c>
+      <c r="D92">
+        <v>4</v>
+      </c>
+      <c r="E92">
+        <v>1221</v>
+      </c>
+      <c r="G92" t="b">
+        <v>0</v>
+      </c>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>66</v>
+      </c>
+      <c r="B93">
+        <v>2</v>
+      </c>
+      <c r="C93" t="s">
+        <v>66</v>
+      </c>
+      <c r="D93">
+        <v>4</v>
+      </c>
+      <c r="E93" t="s">
+        <v>72</v>
+      </c>
+      <c r="F93" t="s">
+        <v>73</v>
+      </c>
+      <c r="G93" t="b">
+        <v>1</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A94" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B94">
+        <v>4</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D94">
+        <v>4</v>
+      </c>
+      <c r="E94" t="s">
+        <v>102</v>
+      </c>
+      <c r="F94" t="s">
+        <v>103</v>
+      </c>
+      <c r="G94" t="b">
+        <v>0</v>
+      </c>
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B95">
+        <v>4</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D95">
+        <v>4</v>
+      </c>
+      <c r="E95" t="s">
+        <v>77</v>
+      </c>
+      <c r="F95" t="s">
+        <v>78</v>
+      </c>
+      <c r="G95" t="b">
+        <v>0</v>
+      </c>
+      <c r="I95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B96">
+        <v>4</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D96">
+        <v>4</v>
+      </c>
+      <c r="E96" t="s">
+        <v>79</v>
+      </c>
+      <c r="G96" t="b">
+        <v>0</v>
+      </c>
+      <c r="I96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A97" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B97">
+        <v>4</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D97">
+        <v>4</v>
+      </c>
+      <c r="E97" t="s">
+        <v>80</v>
+      </c>
+      <c r="G97" t="b">
+        <v>1</v>
+      </c>
+      <c r="H97" t="s">
+        <v>67</v>
+      </c>
+      <c r="I97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>67</v>
+      </c>
+      <c r="B98">
+        <v>4</v>
+      </c>
+      <c r="C98" t="s">
+        <v>67</v>
+      </c>
+      <c r="D98">
+        <v>4</v>
+      </c>
+      <c r="E98">
+        <v>1212</v>
+      </c>
+      <c r="G98" t="b">
+        <v>0</v>
+      </c>
+      <c r="I98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>67</v>
+      </c>
+      <c r="B99">
+        <v>4</v>
+      </c>
+      <c r="C99" t="s">
+        <v>67</v>
+      </c>
+      <c r="D99">
+        <v>4</v>
+      </c>
+      <c r="E99" t="s">
+        <v>81</v>
+      </c>
+      <c r="F99" t="s">
+        <v>82</v>
+      </c>
+      <c r="G99" t="b">
+        <v>0</v>
+      </c>
+      <c r="I99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>67</v>
+      </c>
+      <c r="B100">
+        <v>4</v>
+      </c>
+      <c r="C100" t="s">
+        <v>67</v>
+      </c>
+      <c r="D100">
+        <v>4</v>
+      </c>
+      <c r="E100" t="s">
+        <v>83</v>
+      </c>
+      <c r="G100" t="b">
+        <v>0</v>
+      </c>
+      <c r="I100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>67</v>
+      </c>
+      <c r="B101">
+        <v>4</v>
+      </c>
+      <c r="C101" t="s">
+        <v>67</v>
+      </c>
+      <c r="D101">
+        <v>4</v>
+      </c>
+      <c r="E101" t="s">
+        <v>84</v>
+      </c>
+      <c r="F101" t="s">
+        <v>41</v>
+      </c>
+      <c r="G101" t="b">
+        <v>1</v>
+      </c>
+      <c r="H101" t="s">
+        <v>65</v>
+      </c>
+      <c r="I101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>65</v>
+      </c>
+      <c r="B102">
+        <v>4</v>
+      </c>
+      <c r="C102" t="s">
+        <v>65</v>
+      </c>
+      <c r="D102">
+        <v>4</v>
+      </c>
+      <c r="E102" t="s">
+        <v>86</v>
+      </c>
+      <c r="G102" t="b">
+        <v>0</v>
+      </c>
+      <c r="I102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>65</v>
+      </c>
+      <c r="B103">
+        <v>4</v>
+      </c>
+      <c r="C103" t="s">
+        <v>65</v>
+      </c>
+      <c r="D103">
+        <v>4</v>
+      </c>
+      <c r="E103" t="s">
+        <v>86</v>
+      </c>
+      <c r="G103" t="b">
+        <v>0</v>
+      </c>
+      <c r="I103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>65</v>
+      </c>
+      <c r="B104">
+        <v>4</v>
+      </c>
+      <c r="C104" t="s">
+        <v>65</v>
+      </c>
+      <c r="D104">
+        <v>4</v>
+      </c>
+      <c r="E104" t="s">
+        <v>87</v>
+      </c>
+      <c r="F104" t="s">
+        <v>86</v>
+      </c>
+      <c r="G104" t="b">
+        <v>0</v>
+      </c>
+      <c r="I104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>65</v>
+      </c>
+      <c r="B105">
+        <v>4</v>
+      </c>
+      <c r="C105" t="s">
+        <v>65</v>
+      </c>
+      <c r="D105">
+        <v>4</v>
+      </c>
+      <c r="E105" t="s">
+        <v>47</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G105" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H105" t="s">
+        <v>104</v>
+      </c>
+      <c r="I105" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
